--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>2026年高教社杯全国大学生数学建模竞赛赛题</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -766,15 +766,11 @@
           <t>32</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/27b6e148f8113f09b0269f64a02629fb.html</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -791,7 +787,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -806,7 +802,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -829,11 +825,15 @@
           <t>32</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>关于批准2025—2026年全国大学生数学建模赛题后续研究课题的通告</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/a423b01e1f2ed1a38e9741fc7703ee61.html</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2499,7 +2499,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15858/</t>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3331,14 +3335,14 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>2026年高教社杯全国大学生数学建模竞赛赛题</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3356,23 +3360,15 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
-        </is>
-      </c>
+      <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/27b6e148f8113f09b0269f64a02629fb.html</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3437,14 +3433,14 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SPSSPRO</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3459,18 +3455,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>https://www.spsspro.com/?utm_source=cumcm</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3535,14 +3539,14 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>《数学建模及其应用》</t>
+          <t>SPSSPRO</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3568,7 +3572,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>http://qxyy.cbpt.cnki.net</t>
+          <t>https://www.spsspro.com/?utm_source=cumcm</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3633,14 +3637,14 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中国高校数学建模课程中心</t>
+          <t>《数学建模及其应用》</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3666,7 +3670,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.icourses.cn/</t>
+          <t>http://qxyy.cbpt.cnki.net</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3731,14 +3735,14 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>关于批准2025—2026年全国大学生数学建模赛题后续研究课题的通告</t>
+          <t>中国高校数学建模课程中心</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3764,7 +3768,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/a423b01e1f2ed1a38e9741fc7703ee61.html</t>
+          <t>http://cumcm.icourses.cn/</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3829,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6313,11 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -6385,7 +6393,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6495,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6609,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6723,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6825,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6923,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -728,7 +728,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛赛题</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -766,11 +766,15 @@
           <t>32</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/27b6e148f8113f09b0269f64a02629fb.html</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -787,7 +791,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>2026年全国大学生数学建模竞赛赛题讲评与经验交流会通知</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -802,38 +806,34 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+      <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/74ca2bd675a8399782a41dffa15f0910.html</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2499,11 +2499,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15858/</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3335,14 +3331,14 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026年高教社杯全国大学生数学建模竞赛赛题</t>
+          <t>中国知网</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -3360,15 +3356,23 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026年9月10日</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>https://www.mcm.edu.cn/html_cn/node/27b6e148f8113f09b0269f64a02629fb.html</t>
+          <t>http://cumcm.cnki.net</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3433,14 +3437,14 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>中国知网</t>
+          <t>2026年全国大学生数学建模竞赛赛题讲评与经验交流会通知</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3455,26 +3459,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026年9月10日</t>
-        </is>
-      </c>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>及合作机构 主办： 中国工业与应用数学学会 合作伙伴及独家冠名赞助商： 高等教育出版社 合作网站： 中国大学生在线网站 合作伙伴及服务支持赞助商： 中国知网 赞助单位： 北京大学重</t>
+          <t>“2026年全国大学生数学建模竞赛赛题讲评与经验交流会”</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>http://cumcm.cnki.net</t>
+          <t>https://www.mcm.edu.cn/html_cn/node/74ca2bd675a8399782a41dffa15f0910.html</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6313,11 +6313,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -6393,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2499,7 +2499,11 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15858/</t>
@@ -3095,7 +3099,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3217,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3335,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3441,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3543,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3641,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3935,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4033,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4155,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4253,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4351,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4547,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4645,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4743,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4841,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4939,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5049,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5285,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5407,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5525,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5631,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5749,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5867,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5965,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6083,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6189,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6291,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6317,11 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2009-20</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -6389,7 +6397,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6499,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6613,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6727,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6829,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6927,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -2499,11 +2499,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>https://www.tiaozhanbei.net/article/15858/</t>
@@ -3099,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6317,11 +6313,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>2009-20</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -6397,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/reports/weekly_report.xlsx
+++ b/reports/weekly_report.xlsx
@@ -1921,12 +1921,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
